--- a/ig/nr-add-MS-device-method/StructureDefinition-mesures-observation-head-circumference.xlsx
+++ b/ig/nr-add-MS-device-method/StructureDefinition-mesures-observation-head-circumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:47:06+00:00</t>
+    <t>2023-11-28T13:04:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -440,11 +440,11 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.</t>
-  </si>
-  <si>
     <t>Uri identifiant les systèmes tiers ayant envoyé la ressource.
 L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
